--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322529</v>
+        <v>124322548</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338150</v>
+        <v>338376</v>
       </c>
       <c r="R3" t="n">
-        <v>6532727</v>
+        <v>6532725</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322548</v>
+        <v>124322529</v>
       </c>
       <c r="B4" t="n">
         <v>100279</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338376</v>
+        <v>338150</v>
       </c>
       <c r="R4" t="n">
-        <v>6532725</v>
+        <v>6532727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322548</v>
+        <v>124322529</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338376</v>
+        <v>338150</v>
       </c>
       <c r="R3" t="n">
-        <v>6532725</v>
+        <v>6532727</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322529</v>
+        <v>124322548</v>
       </c>
       <c r="B4" t="n">
         <v>100279</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338150</v>
+        <v>338376</v>
       </c>
       <c r="R4" t="n">
-        <v>6532727</v>
+        <v>6532725</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,6 +989,832 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128465331</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95807</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>338316</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6532681</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128465352</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95924</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>210</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>338231</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6532765</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128465344</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>338272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6532684</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128465326</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95807</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>338392</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6532745</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128465324</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8364</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>338393</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6532741</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128465330</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95828</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>338323</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6532727</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128465350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95828</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>338231</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6532765</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128465328</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95828</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>338350</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6532736</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95807</v>
+        <v>95809</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>95924</v>
+        <v>95926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92352</v>
+        <v>92354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95807</v>
+        <v>95809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95828</v>
+        <v>95830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95828</v>
+        <v>95830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95828</v>
+        <v>95830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92354</v>
+        <v>92446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>95926</v>
+        <v>96019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95902</v>
+        <v>95908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96019</v>
+        <v>96025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92446</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95902</v>
+        <v>95908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95923</v>
+        <v>95929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95923</v>
+        <v>95929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95923</v>
+        <v>95929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95908</v>
+        <v>95914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96025</v>
+        <v>96031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95908</v>
+        <v>95914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95929</v>
+        <v>95935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95929</v>
+        <v>95935</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95929</v>
+        <v>95935</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96031</v>
+        <v>96033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92458</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95916</v>
+        <v>95917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95916</v>
+        <v>95917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95937</v>
+        <v>95938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95937</v>
+        <v>95938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95937</v>
+        <v>95938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95917</v>
+        <v>95944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96034</v>
+        <v>96061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92461</v>
+        <v>92488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95917</v>
+        <v>95944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95938</v>
+        <v>95965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95938</v>
+        <v>95965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95938</v>
+        <v>95965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,6 +1815,706 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128877053</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>338456</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6532864</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128877050</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8364</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>338436</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6532755</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128877008</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92801</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>338315</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6532650</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128877036</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>338215</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6532807</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128877052</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95971</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>338432</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6532758</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128877048</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100813</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>338392</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6532722</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128877040</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92801</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>338281</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6532676</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95944</v>
+        <v>95957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96061</v>
+        <v>96074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92488</v>
+        <v>92498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95944</v>
+        <v>95957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95965</v>
+        <v>95978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95965</v>
+        <v>95978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95965</v>
+        <v>95978</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95950</v>
+        <v>95957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>95971</v>
+        <v>95978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>95978</v>
+        <v>95982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92498</v>
+        <v>92502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95957</v>
+        <v>95961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95978</v>
+        <v>95982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95978</v>
+        <v>95982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95978</v>
+        <v>95982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>128465331</v>
       </c>
       <c r="B5" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128465352</v>
       </c>
       <c r="B6" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128465344</v>
       </c>
       <c r="B7" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128465326</v>
       </c>
       <c r="B8" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128465330</v>
       </c>
       <c r="B10" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128465350</v>
       </c>
       <c r="B11" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>128465328</v>
       </c>
       <c r="B12" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95961</v>
+        <v>95968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>95982</v>
+        <v>95989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95976</v>
+        <v>95981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>95997</v>
+        <v>96002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95981</v>
+        <v>95984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96002</v>
+        <v>96005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95984</v>
+        <v>95994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96005</v>
+        <v>96015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96015</v>
+        <v>96022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>96001</v>
+        <v>96003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>96003</v>
+        <v>96029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>96029</v>
+        <v>96030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>96030</v>
+        <v>96031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>128877053</v>
       </c>
       <c r="B13" t="n">
-        <v>96031</v>
+        <v>96035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128877008</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128877036</v>
       </c>
       <c r="B16" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128877052</v>
       </c>
       <c r="B17" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>128877048</v>
       </c>
       <c r="B18" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>128877040</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124272786</v>
+        <v>128465332</v>
       </c>
       <c r="B2" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338336</v>
+        <v>338323</v>
       </c>
       <c r="R2" t="n">
-        <v>6532768</v>
+        <v>6532669</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera ställen på ön.</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Niklasson, Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124322529</v>
+        <v>128465352</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338150</v>
+        <v>338231</v>
       </c>
       <c r="R3" t="n">
-        <v>6532727</v>
+        <v>6532765</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -882,60 +877,59 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124322548</v>
+        <v>124272739</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Knaben</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338376</v>
+        <v>338162</v>
       </c>
       <c r="R4" t="n">
-        <v>6532725</v>
+        <v>6532766</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,28 +967,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson</t>
+          <t>Anders Niklasson, Anton Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128465331</v>
+        <v>128465333</v>
       </c>
       <c r="B5" t="n">
-        <v>95971</v>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338316</v>
+        <v>338321</v>
       </c>
       <c r="R5" t="n">
-        <v>6532681</v>
+        <v>6532673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128465352</v>
+        <v>124322531</v>
       </c>
       <c r="B6" t="n">
-        <v>96088</v>
+        <v>96439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338231</v>
+        <v>338162</v>
       </c>
       <c r="R6" t="n">
-        <v>6532765</v>
+        <v>6532776</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,21 +1164,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1193,17 +1173,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128465344</v>
+        <v>124322543</v>
       </c>
       <c r="B7" t="n">
-        <v>92510</v>
+        <v>96439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5836</v>
+        <v>2666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338272</v>
+        <v>338264</v>
       </c>
       <c r="R7" t="n">
-        <v>6532684</v>
+        <v>6532709</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,17 +1270,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128465326</v>
+        <v>124322571</v>
       </c>
       <c r="B8" t="n">
-        <v>95971</v>
+        <v>96439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,16 +1288,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1332,7 +1312,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338392</v>
+        <v>338086</v>
       </c>
       <c r="R8" t="n">
         <v>6532745</v>
@@ -1362,12 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,57 +1367,52 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128465324</v>
+        <v>124322532</v>
       </c>
       <c r="B9" t="n">
-        <v>8364</v>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338393</v>
+        <v>338162</v>
       </c>
       <c r="R9" t="n">
-        <v>6532741</v>
+        <v>6532776</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,12 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,21 +1455,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1504,17 +1464,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128465330</v>
+        <v>128465326</v>
       </c>
       <c r="B10" t="n">
-        <v>95992</v>
+        <v>96437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338323</v>
+        <v>338392</v>
       </c>
       <c r="R10" t="n">
-        <v>6532727</v>
+        <v>6532745</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128465350</v>
+        <v>128465331</v>
       </c>
       <c r="B11" t="n">
-        <v>95992</v>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338231</v>
+        <v>338316</v>
       </c>
       <c r="R11" t="n">
-        <v>6532765</v>
+        <v>6532681</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1689,21 +1649,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1720,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128465328</v>
+        <v>128465349</v>
       </c>
       <c r="B12" t="n">
-        <v>95992</v>
+        <v>96437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>338350</v>
+        <v>338281</v>
       </c>
       <c r="R12" t="n">
-        <v>6532736</v>
+        <v>6532716</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128877053</v>
+        <v>128465356</v>
       </c>
       <c r="B13" t="n">
-        <v>96035</v>
+        <v>96437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>338456</v>
+        <v>338187</v>
       </c>
       <c r="R13" t="n">
-        <v>6532864</v>
+        <v>6532760</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1882,12 +1827,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,57 +1852,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128877050</v>
+        <v>128877013</v>
       </c>
       <c r="B14" t="n">
-        <v>8364</v>
+        <v>96437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106540</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skuggetorpsön, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>338436</v>
+        <v>338138</v>
       </c>
       <c r="R14" t="n">
-        <v>6532755</v>
+        <v>6532778</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2000,21 +1940,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2031,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128877008</v>
+        <v>128877043</v>
       </c>
       <c r="B15" t="n">
-        <v>92837</v>
+        <v>96437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>338315</v>
+        <v>338305</v>
       </c>
       <c r="R15" t="n">
-        <v>6532650</v>
+        <v>6532643</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2128,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128877036</v>
+        <v>124322530</v>
       </c>
       <c r="B16" t="n">
-        <v>100899</v>
+        <v>96186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338215</v>
+        <v>338162</v>
       </c>
       <c r="R16" t="n">
-        <v>6532807</v>
+        <v>6532776</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2193,12 +2118,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,17 +2143,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128877052</v>
+        <v>128465346</v>
       </c>
       <c r="B17" t="n">
-        <v>96056</v>
+        <v>96186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>2676</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>338432</v>
+        <v>338272</v>
       </c>
       <c r="R17" t="n">
-        <v>6532758</v>
+        <v>6532712</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2290,12 +2215,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2304,7 +2229,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2316,17 +2240,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128877048</v>
+        <v>128465354</v>
       </c>
       <c r="B18" t="n">
-        <v>100899</v>
+        <v>96186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2334,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2676</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2358,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>338392</v>
+        <v>338201</v>
       </c>
       <c r="R18" t="n">
-        <v>6532722</v>
+        <v>6532753</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,12 +2312,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,17 +2337,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128877040</v>
+        <v>128465358</v>
       </c>
       <c r="B19" t="n">
-        <v>92837</v>
+        <v>96186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2431,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>2676</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>338281</v>
+        <v>338167</v>
       </c>
       <c r="R19" t="n">
-        <v>6532676</v>
+        <v>6532773</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2485,12 +2409,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2510,10 +2434,2924 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128877014</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96186</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>338138</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6532778</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124322570</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>338087</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6532744</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128465328</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>338350</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6532736</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128465330</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>338323</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6532727</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128465350</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>338231</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6532765</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128877004</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>338500</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6532682</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128877052</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>338432</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6532758</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128465363</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>338092</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6532706</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128465335</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>338329</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6532645</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128877008</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>338315</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6532650</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128877040</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>338281</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6532676</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128465353</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>338208</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6532767</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128465344</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>338272</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6532684</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128465348</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>338286</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6532712</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128465357</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>338183</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6532759</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128465324</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8369</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>338393</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6532741</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson, Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128877050</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8369</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>338436</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6532755</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124272786</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>338336</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6532768</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På flera ställen på ön.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Niklasson, Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128877007</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>338332</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6532629</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128877009</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>338325</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6532655</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124322529</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>338150</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6532727</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124322547</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>338323</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6532690</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124322548</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>338376</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6532725</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124322572</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>338119</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6532690</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128877036</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>338215</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6532807</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128877047</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>338365</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6532691</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128877048</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>338392</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6532722</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128877003</v>
+      </c>
+      <c r="B47" t="n">
+        <v>85534</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>241</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>338380</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6532826</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128877053</v>
+      </c>
+      <c r="B48" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skuggetorpsön, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>338456</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6532864</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7086-2025 artfynd.xlsx
+++ b/artfynd/A 7086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465333</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322531</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322543</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322532</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465326</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465331</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465349</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465356</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877013</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877043</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877053</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322530</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465346</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465358</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877014</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322570</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465328</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465330</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3147,6 +3272,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465350</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3244,6 +3374,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877004</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3342,6 +3477,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877052</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3439,6 +3579,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465363</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3536,6 +3681,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3633,6 +3783,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877008</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3730,6 +3885,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877040</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3827,6 +3987,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465353</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3924,6 +4089,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465344</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4021,6 +4191,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465348</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4138,6 +4313,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465357</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4255,6 +4435,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465324</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4372,6 +4557,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4479,6 +4669,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124272786</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4576,6 +4771,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877007</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4673,6 +4873,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877009</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4770,6 +4975,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322529</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4867,6 +5077,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322547</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4964,6 +5179,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322548</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5061,6 +5281,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322572</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5158,6 +5383,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877036</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5255,6 +5485,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5352,8 +5587,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128877048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>